--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E8B6EF5-7D2C-43E9-94FF-2D450822DA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB479394-C89F-498A-BE73-20DF9E31E167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -684,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -724,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -830,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -972,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -980,13 +977,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16" width="5.625" customWidth="1"/>
+    <col min="1" max="17" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0</v>
       </c>
@@ -1027,7 +1024,7 @@
         <v>420</v>
       </c>
       <c r="M1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N1">
         <v>0</v>
@@ -1038,8 +1035,11 @@
       <c r="P1">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>420</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -1091,8 +1091,11 @@
       <c r="P2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>220</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -1144,8 +1147,11 @@
       <c r="P3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1186,7 +1192,7 @@
         <v>200</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1197,8 +1203,11 @@
       <c r="P4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1239,7 +1248,7 @@
         <v>420</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1250,8 +1259,11 @@
       <c r="P5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>70</v>
       </c>
@@ -1292,7 +1304,7 @@
         <v>60</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -1303,8 +1315,11 @@
       <c r="P6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>-70</v>
       </c>
@@ -1345,7 +1360,7 @@
         <v>60</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -1356,8 +1371,11 @@
       <c r="P7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>0</v>
       </c>
@@ -1398,7 +1416,7 @@
         <v>60</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -1409,8 +1427,11 @@
       <c r="P8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0</v>
       </c>
@@ -1451,7 +1472,7 @@
         <v>80</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1462,8 +1483,11 @@
       <c r="P9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0</v>
       </c>
@@ -1504,7 +1528,7 @@
         <v>80</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1515,8 +1539,11 @@
       <c r="P10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>0</v>
       </c>
@@ -1557,7 +1584,7 @@
         <v>80</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1568,8 +1595,11 @@
       <c r="P11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>0</v>
       </c>
@@ -1610,7 +1640,7 @@
         <v>20</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1621,8 +1651,11 @@
       <c r="P12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>0</v>
       </c>
@@ -1663,7 +1696,7 @@
         <v>420</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1674,8 +1707,11 @@
       <c r="P13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>0</v>
       </c>
@@ -1716,7 +1752,7 @@
         <v>500</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1727,8 +1763,11 @@
       <c r="P14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>0</v>
       </c>
@@ -1769,19 +1808,22 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>320</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>-2660</v>
       </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>0</v>
       </c>
@@ -1822,7 +1864,7 @@
         <v>420</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1833,8 +1875,11 @@
       <c r="P16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>310</v>
       </c>
@@ -1875,7 +1920,7 @@
         <v>200</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1886,8 +1931,11 @@
       <c r="P17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>730</v>
       </c>
@@ -1928,7 +1976,7 @@
         <v>200</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -1939,8 +1987,11 @@
       <c r="P18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1090</v>
       </c>
@@ -1981,7 +2032,7 @@
         <v>200</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -1992,8 +2043,11 @@
       <c r="P19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>950</v>
       </c>
@@ -2034,7 +2088,7 @@
         <v>200</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2045,8 +2099,11 @@
       <c r="P20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>990</v>
       </c>
@@ -2087,19 +2144,22 @@
         <v>60</v>
       </c>
       <c r="M21">
+        <v>-1</v>
+      </c>
+      <c r="N21">
         <v>990</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>320</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>-3100</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>990</v>
       </c>
@@ -2140,19 +2200,22 @@
         <v>60</v>
       </c>
       <c r="M22">
+        <v>-1</v>
+      </c>
+      <c r="N22">
         <v>990</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>200</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>-2960</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>990</v>
       </c>
@@ -2193,7 +2256,7 @@
         <v>80</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -2204,8 +2267,11 @@
       <c r="P23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1230</v>
       </c>
@@ -2246,7 +2312,7 @@
         <v>200</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -2257,8 +2323,11 @@
       <c r="P24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>1030</v>
       </c>
@@ -2299,7 +2368,7 @@
         <v>80</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -2310,8 +2379,11 @@
       <c r="P25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1050</v>
       </c>
@@ -2352,7 +2424,7 @@
         <v>80</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -2363,8 +2435,11 @@
       <c r="P26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27">
         <f>A26+20</f>
         <v>1070</v>
@@ -2406,7 +2481,7 @@
         <v>80</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -2417,8 +2492,11 @@
       <c r="P27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28">
         <f t="shared" ref="A28:A34" si="7">A27+20</f>
         <v>1090</v>
@@ -2460,7 +2538,7 @@
         <v>80</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -2471,8 +2549,11 @@
       <c r="P28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29">
         <f t="shared" si="7"/>
         <v>1110</v>
@@ -2514,7 +2595,7 @@
         <v>80</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -2525,8 +2606,11 @@
       <c r="P29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30">
         <f t="shared" si="7"/>
         <v>1130</v>
@@ -2568,7 +2652,7 @@
         <v>80</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -2579,8 +2663,11 @@
       <c r="P30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31">
         <f t="shared" si="7"/>
         <v>1150</v>
@@ -2622,7 +2709,7 @@
         <v>80</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -2633,8 +2720,11 @@
       <c r="P31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32">
         <f t="shared" si="7"/>
         <v>1170</v>
@@ -2676,7 +2766,7 @@
         <v>80</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -2687,8 +2777,11 @@
       <c r="P32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A33">
         <f t="shared" si="7"/>
         <v>1190</v>
@@ -2730,7 +2823,7 @@
         <v>80</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -2741,8 +2834,11 @@
       <c r="P33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A34">
         <f t="shared" si="7"/>
         <v>1210</v>
@@ -2784,7 +2880,7 @@
         <v>80</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -2795,8 +2891,11 @@
       <c r="P34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>1450</v>
       </c>
@@ -2837,7 +2936,7 @@
         <v>200</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -2848,8 +2947,11 @@
       <c r="P35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>1610</v>
       </c>
@@ -2890,19 +2992,22 @@
         <v>100</v>
       </c>
       <c r="M36">
+        <v>-1</v>
+      </c>
+      <c r="N36">
         <v>2610</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>320</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>-3180</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>1.5</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>2610</v>
       </c>
@@ -2944,20 +3049,23 @@
         <v>100</v>
       </c>
       <c r="M37">
+        <v>-1</v>
+      </c>
+      <c r="N37">
         <v>1610</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>320</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <f>-2880</f>
         <v>-2880</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>1.5</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>2770</v>
       </c>
@@ -2998,7 +3106,7 @@
         <v>200</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -3009,8 +3117,11 @@
       <c r="P38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>3480</v>
       </c>
@@ -3051,7 +3162,7 @@
         <v>1000</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -3062,8 +3173,11 @@
       <c r="P39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>4030</v>
       </c>
@@ -3104,7 +3218,7 @@
         <v>100</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -3115,8 +3229,11 @@
       <c r="P40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>4030</v>
       </c>
@@ -3157,7 +3274,7 @@
         <v>20</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -3168,8 +3285,11 @@
       <c r="P41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>0</v>
       </c>
@@ -3208,7 +3328,7 @@
         <v>420</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -3219,8 +3339,11 @@
       <c r="P42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>0</v>
       </c>
@@ -3259,7 +3382,7 @@
         <v>420</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -3270,8 +3393,11 @@
       <c r="P43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>1450</v>
       </c>
@@ -3310,7 +3436,7 @@
         <v>200</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -3321,8 +3447,11 @@
       <c r="P44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>2770</v>
       </c>
@@ -3361,7 +3490,7 @@
         <v>200</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -3372,8 +3501,11 @@
       <c r="P45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>0</v>
       </c>
@@ -3414,7 +3546,7 @@
         <v>20</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -3425,8 +3557,11 @@
       <c r="P46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>110</v>
       </c>
@@ -3467,7 +3602,7 @@
         <v>2120</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N47">
         <v>0</v>
@@ -3478,8 +3613,11 @@
       <c r="P47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>-110</v>
       </c>
@@ -3520,7 +3658,7 @@
         <v>2120</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N48">
         <v>0</v>
@@ -3531,8 +3669,11 @@
       <c r="P48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>185</v>
       </c>
@@ -3573,7 +3714,7 @@
         <v>20</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N49">
         <v>0</v>
@@ -3584,8 +3725,11 @@
       <c r="P49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>-185</v>
       </c>
@@ -3626,7 +3770,7 @@
         <v>20</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N50">
         <v>0</v>
@@ -3637,8 +3781,11 @@
       <c r="P50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>-260</v>
       </c>
@@ -3679,7 +3826,7 @@
         <v>500</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N51">
         <v>0</v>
@@ -3690,8 +3837,11 @@
       <c r="P51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>260</v>
       </c>
@@ -3732,7 +3882,7 @@
         <v>500</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N52">
         <v>0</v>
@@ -3743,8 +3893,11 @@
       <c r="P52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>0</v>
       </c>
@@ -3785,7 +3938,7 @@
         <v>20</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N53">
         <v>0</v>
@@ -3796,8 +3949,11 @@
       <c r="P53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>0</v>
       </c>
@@ -3838,7 +3994,7 @@
         <v>20</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N54">
         <v>0</v>
@@ -3849,8 +4005,11 @@
       <c r="P54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>110</v>
       </c>
@@ -3891,7 +4050,7 @@
         <v>220</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N55">
         <v>0</v>
@@ -3902,8 +4061,11 @@
       <c r="P55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>-110</v>
       </c>
@@ -3944,7 +4106,7 @@
         <v>420</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -3955,8 +4117,11 @@
       <c r="P56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>780</v>
       </c>
@@ -3997,7 +4162,7 @@
         <v>20</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N57">
         <v>0</v>
@@ -4008,8 +4173,11 @@
       <c r="P57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>890</v>
       </c>
@@ -4050,7 +4218,7 @@
         <v>20</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -4061,8 +4229,11 @@
       <c r="P58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>1670</v>
       </c>
@@ -4103,7 +4274,7 @@
         <v>200</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -4114,8 +4285,11 @@
       <c r="P59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>2550</v>
       </c>
@@ -4156,7 +4330,7 @@
         <v>200</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -4167,8 +4341,11 @@
       <c r="P60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>2770</v>
       </c>
@@ -4209,7 +4386,7 @@
         <v>20</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N61">
         <v>0</v>
@@ -4220,8 +4397,11 @@
       <c r="P61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>2770</v>
       </c>
@@ -4262,7 +4442,7 @@
         <v>20</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -4273,8 +4453,11 @@
       <c r="P62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>2970</v>
       </c>
@@ -4315,7 +4498,7 @@
         <v>380</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N63">
         <v>0</v>
@@ -4326,8 +4509,11 @@
       <c r="P63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>2970</v>
       </c>
@@ -4368,7 +4554,7 @@
         <v>380</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -4379,8 +4565,11 @@
       <c r="P64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>3480</v>
       </c>
@@ -4421,7 +4610,7 @@
         <v>20</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -4432,8 +4621,11 @@
       <c r="P65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>3480</v>
       </c>
@@ -4474,7 +4666,7 @@
         <v>20</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N66">
         <v>0</v>
@@ -4485,8 +4677,11 @@
       <c r="P66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>3990</v>
       </c>
@@ -4527,7 +4722,7 @@
         <v>1000</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -4538,16 +4733,19 @@
       <c r="P67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>0</v>
       </c>
       <c r="B68">
-        <v>-1000</v>
+        <v>200</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>-2120</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -4559,28 +4757,28 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I68">
         <v>1</v>
       </c>
       <c r="J68">
         <f t="shared" si="20"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K68">
         <f t="shared" si="21"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L68">
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -4591,16 +4789,19 @@
       <c r="P68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>0</v>
       </c>
       <c r="B69">
-        <v>-1000</v>
+        <v>200</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4612,28 +4813,28 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I69">
         <v>1</v>
       </c>
       <c r="J69">
         <f t="shared" si="20"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K69">
         <f t="shared" si="21"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L69">
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N69">
         <v>0</v>
@@ -4644,16 +4845,19 @@
       <c r="P69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>0</v>
       </c>
       <c r="B70">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4686,7 +4890,7 @@
         <v>20</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N70">
         <v>0</v>
@@ -4697,8 +4901,11 @@
       <c r="P70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>0</v>
       </c>
@@ -4739,7 +4946,7 @@
         <v>20</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N71">
         <v>0</v>
@@ -4750,8 +4957,11 @@
       <c r="P71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>0</v>
       </c>
@@ -4792,7 +5002,7 @@
         <v>20</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -4803,8 +5013,11 @@
       <c r="P72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>0</v>
       </c>
@@ -4845,7 +5058,7 @@
         <v>20</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -4856,8 +5069,11 @@
       <c r="P73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>0</v>
       </c>
@@ -4898,7 +5114,7 @@
         <v>20</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N74">
         <v>0</v>
@@ -4909,8 +5125,11 @@
       <c r="P74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>0</v>
       </c>
@@ -4951,7 +5170,7 @@
         <v>20</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -4962,8 +5181,11 @@
       <c r="P75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>0</v>
       </c>
@@ -5004,7 +5226,7 @@
         <v>20</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N76">
         <v>0</v>
@@ -5015,8 +5237,11 @@
       <c r="P76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>0</v>
       </c>
@@ -5057,7 +5282,7 @@
         <v>20</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N77">
         <v>0</v>
@@ -5068,8 +5293,11 @@
       <c r="P77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>0</v>
       </c>
@@ -5110,7 +5338,7 @@
         <v>20</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N78">
         <v>0</v>
@@ -5121,8 +5349,11 @@
       <c r="P78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>0</v>
       </c>
@@ -5163,7 +5394,7 @@
         <v>20</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N79">
         <v>0</v>
@@ -5174,8 +5405,11 @@
       <c r="P79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>0</v>
       </c>
@@ -5216,7 +5450,7 @@
         <v>20</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N80">
         <v>0</v>
@@ -5227,8 +5461,11 @@
       <c r="P80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>0</v>
       </c>
@@ -5269,7 +5506,7 @@
         <v>20</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N81">
         <v>0</v>
@@ -5280,8 +5517,11 @@
       <c r="P81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>0</v>
       </c>
@@ -5322,7 +5562,7 @@
         <v>20</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N82">
         <v>0</v>
@@ -5333,8 +5573,11 @@
       <c r="P82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>0</v>
       </c>
@@ -5375,7 +5618,7 @@
         <v>20</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N83">
         <v>0</v>
@@ -5386,8 +5629,11 @@
       <c r="P83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>0</v>
       </c>
@@ -5428,7 +5674,7 @@
         <v>20</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N84">
         <v>0</v>
@@ -5439,8 +5685,11 @@
       <c r="P84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>0</v>
       </c>
@@ -5481,7 +5730,7 @@
         <v>20</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N85">
         <v>0</v>
@@ -5492,8 +5741,11 @@
       <c r="P85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>0</v>
       </c>
@@ -5534,7 +5786,7 @@
         <v>20</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N86">
         <v>0</v>
@@ -5545,8 +5797,11 @@
       <c r="P86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>0</v>
       </c>
@@ -5587,7 +5842,7 @@
         <v>20</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N87">
         <v>0</v>
@@ -5598,8 +5853,11 @@
       <c r="P87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>0</v>
       </c>
@@ -5640,7 +5898,7 @@
         <v>20</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N88">
         <v>0</v>
@@ -5651,8 +5909,11 @@
       <c r="P88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>0</v>
       </c>
@@ -5693,7 +5954,7 @@
         <v>20</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N89">
         <v>0</v>
@@ -5704,8 +5965,11 @@
       <c r="P89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>0</v>
       </c>
@@ -5746,7 +6010,7 @@
         <v>20</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N90">
         <v>0</v>
@@ -5757,8 +6021,11 @@
       <c r="P90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>0</v>
       </c>
@@ -5799,7 +6066,7 @@
         <v>20</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N91">
         <v>0</v>
@@ -5810,8 +6077,11 @@
       <c r="P91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>0</v>
       </c>
@@ -5852,7 +6122,7 @@
         <v>20</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N92">
         <v>0</v>
@@ -5863,8 +6133,11 @@
       <c r="P92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>0</v>
       </c>
@@ -5905,7 +6178,7 @@
         <v>20</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N93">
         <v>0</v>
@@ -5916,8 +6189,11 @@
       <c r="P93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>0</v>
       </c>
@@ -5958,7 +6234,7 @@
         <v>20</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N94">
         <v>0</v>
@@ -5969,8 +6245,11 @@
       <c r="P94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>0</v>
       </c>
@@ -6011,7 +6290,7 @@
         <v>20</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N95">
         <v>0</v>
@@ -6022,8 +6301,11 @@
       <c r="P95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>0</v>
       </c>
@@ -6064,7 +6346,7 @@
         <v>20</v>
       </c>
       <c r="M96">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N96">
         <v>0</v>
@@ -6075,8 +6357,11 @@
       <c r="P96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>0</v>
       </c>
@@ -6117,7 +6402,7 @@
         <v>20</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N97">
         <v>0</v>
@@ -6128,8 +6413,11 @@
       <c r="P97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0</v>
       </c>
@@ -6170,7 +6458,7 @@
         <v>20</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N98">
         <v>0</v>
@@ -6181,8 +6469,11 @@
       <c r="P98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0</v>
       </c>
@@ -6223,7 +6514,7 @@
         <v>20</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N99">
         <v>0</v>
@@ -6234,8 +6525,11 @@
       <c r="P99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="Q99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0</v>
       </c>
@@ -6276,7 +6570,7 @@
         <v>20</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N100">
         <v>0</v>
@@ -6285,6 +6579,9 @@
         <v>0</v>
       </c>
       <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB479394-C89F-498A-BE73-20DF9E31E167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F3CCD3-49EC-45F5-A7DB-8AB593EF34D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1068,15 +1068,15 @@
         <v>21</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J63" si="1">G2*20</f>
+        <f t="shared" ref="J2:J61" si="1">G2*20</f>
         <v>200</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K63" si="2">H2*20</f>
+        <f t="shared" ref="K2:K61" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L63" si="3">I2*20</f>
+        <f t="shared" ref="L2:L61" si="3">I2*20</f>
         <v>420</v>
       </c>
       <c r="M2">
@@ -3899,13 +3899,13 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="B53">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="C53">
-        <v>-2620</v>
+        <v>-2820</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3917,25 +3917,25 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J53">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="K53">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="L53">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="M53">
         <v>-1</v>
@@ -3955,13 +3955,13 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A54">
-        <v>0</v>
+        <v>-110</v>
       </c>
       <c r="B54">
         <v>450</v>
       </c>
       <c r="C54">
-        <v>-2700</v>
+        <v>-2920</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3973,17 +3973,17 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>12.5</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J54">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="K54">
         <f t="shared" si="2"/>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="L54">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="M54">
         <v>-1</v>
@@ -4011,13 +4011,13 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>110</v>
+        <v>780</v>
       </c>
       <c r="B55">
         <v>450</v>
       </c>
       <c r="C55">
-        <v>-2820</v>
+        <v>-3140</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -4029,17 +4029,17 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="H55">
         <v>12.5</v>
       </c>
       <c r="I55">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J55">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>1760</v>
       </c>
       <c r="K55">
         <f t="shared" si="2"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="L55">
         <f t="shared" si="3"/>
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="M55">
         <v>-1</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>-110</v>
+        <v>890</v>
       </c>
       <c r="B56">
         <v>450</v>
@@ -4085,17 +4085,17 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="H56">
         <v>12.5</v>
       </c>
       <c r="I56">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J56">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>1540</v>
       </c>
       <c r="K56">
         <f t="shared" si="2"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="L56">
         <f t="shared" si="3"/>
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="M56">
         <v>-1</v>
@@ -4123,13 +4123,13 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>780</v>
+        <v>1670</v>
       </c>
       <c r="B57">
         <v>450</v>
       </c>
       <c r="C57">
-        <v>-3140</v>
+        <v>-3030</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -4141,17 +4141,17 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>12.5</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J57">
         <f t="shared" si="1"/>
-        <v>1760</v>
+        <v>20</v>
       </c>
       <c r="K57">
         <f t="shared" si="2"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="L57">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M57">
         <v>-1</v>
@@ -4179,13 +4179,13 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>890</v>
+        <v>2550</v>
       </c>
       <c r="B58">
         <v>450</v>
       </c>
       <c r="C58">
-        <v>-2920</v>
+        <v>-3030</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -4197,17 +4197,17 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="H58">
         <v>12.5</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J58">
         <f t="shared" si="1"/>
-        <v>1540</v>
+        <v>20</v>
       </c>
       <c r="K58">
         <f t="shared" si="2"/>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="L58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M58">
         <v>-1</v>
@@ -4235,13 +4235,13 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>1670</v>
+        <v>2770</v>
       </c>
       <c r="B59">
         <v>450</v>
       </c>
       <c r="C59">
-        <v>-3030</v>
+        <v>-2920</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -4253,17 +4253,17 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H59">
         <v>12.5</v>
       </c>
       <c r="I59">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K59">
         <f t="shared" si="2"/>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="L59">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="M59">
         <v>-1</v>
@@ -4291,13 +4291,13 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>2550</v>
+        <v>2770</v>
       </c>
       <c r="B60">
         <v>450</v>
       </c>
       <c r="C60">
-        <v>-3030</v>
+        <v>-3140</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -4309,17 +4309,17 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H60">
         <v>12.5</v>
       </c>
       <c r="I60">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J60">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K60">
         <f t="shared" si="2"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="L60">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="M60">
         <v>-1</v>
@@ -4347,13 +4347,13 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>2770</v>
+        <v>2970</v>
       </c>
       <c r="B61">
         <v>450</v>
       </c>
       <c r="C61">
-        <v>-2920</v>
+        <v>-2720</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -4365,17 +4365,17 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>12.5</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J61">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="K61">
         <f t="shared" si="2"/>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="L61">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="M61">
         <v>-1</v>
@@ -4403,13 +4403,13 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>2770</v>
+        <v>2970</v>
       </c>
       <c r="B62">
         <v>450</v>
       </c>
       <c r="C62">
-        <v>-3140</v>
+        <v>-3340</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -4421,25 +4421,25 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H62">
         <v>12.5</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J62">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <f t="shared" ref="J62:J95" si="20">G62*20</f>
+        <v>20</v>
       </c>
       <c r="K62">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K62:K95" si="21">H62*20</f>
         <v>250</v>
       </c>
       <c r="L62">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f t="shared" ref="L62:L95" si="22">I62*20</f>
+        <v>380</v>
       </c>
       <c r="M62">
         <v>-1</v>
@@ -4459,13 +4459,13 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>2970</v>
+        <v>3480</v>
       </c>
       <c r="B63">
         <v>450</v>
       </c>
       <c r="C63">
-        <v>-2720</v>
+        <v>-2520</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -4477,25 +4477,25 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H63">
         <v>12.5</v>
       </c>
       <c r="I63">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="20"/>
+        <v>1000</v>
       </c>
       <c r="K63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="21"/>
         <v>250</v>
       </c>
       <c r="L63">
-        <f t="shared" si="3"/>
-        <v>380</v>
+        <f t="shared" si="22"/>
+        <v>20</v>
       </c>
       <c r="M63">
         <v>-1</v>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>2970</v>
+        <v>3480</v>
       </c>
       <c r="B64">
         <v>450</v>
       </c>
       <c r="C64">
-        <v>-3340</v>
+        <v>-3540</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -4533,25 +4533,25 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H64">
         <v>12.5</v>
       </c>
       <c r="I64">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J98" si="20">G64*20</f>
-        <v>20</v>
+        <f t="shared" si="20"/>
+        <v>1000</v>
       </c>
       <c r="K64">
-        <f t="shared" ref="K64:K98" si="21">H64*20</f>
+        <f t="shared" si="21"/>
         <v>250</v>
       </c>
       <c r="L64">
-        <f t="shared" ref="L64:L98" si="22">I64*20</f>
-        <v>380</v>
+        <f t="shared" si="22"/>
+        <v>20</v>
       </c>
       <c r="M64">
         <v>-1</v>
@@ -4571,13 +4571,13 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>3480</v>
+        <v>0</v>
       </c>
       <c r="B65">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="C65">
-        <v>-2520</v>
+        <v>-2600</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -4589,28 +4589,28 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H65">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" si="20"/>
-        <v>1000</v>
+        <f t="shared" ref="J65:J66" si="23">G65*20</f>
+        <v>500</v>
       </c>
       <c r="K65">
-        <f t="shared" si="21"/>
-        <v>250</v>
+        <f t="shared" ref="K65:K66" si="24">H65*20</f>
+        <v>100</v>
       </c>
       <c r="L65">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="L65:L66" si="25">I65*20</f>
         <v>20</v>
       </c>
       <c r="M65">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -4627,13 +4627,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>3480</v>
+        <v>3990</v>
       </c>
       <c r="B66">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C66">
-        <v>-3540</v>
+        <v>-3030</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4645,28 +4645,28 @@
         <v>0</v>
       </c>
       <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66">
         <v>50</v>
       </c>
-      <c r="H66">
-        <v>12.5</v>
-      </c>
-      <c r="I66">
-        <v>1</v>
-      </c>
       <c r="J66">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="24"/>
+        <v>100</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="25"/>
         <v>1000</v>
       </c>
-      <c r="K66">
-        <f t="shared" si="21"/>
-        <v>250</v>
-      </c>
-      <c r="L66">
-        <f t="shared" si="22"/>
-        <v>20</v>
-      </c>
       <c r="M66">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N66">
         <v>0</v>
@@ -4683,13 +4683,13 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>3990</v>
+        <v>0</v>
       </c>
       <c r="B67">
-        <v>450</v>
+        <v>-1000</v>
       </c>
       <c r="C67">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -4704,22 +4704,22 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="J67" si="26">G67*20</f>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="21"/>
-        <v>250</v>
+        <f t="shared" ref="K67" si="27">H67*20</f>
+        <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="22"/>
-        <v>1000</v>
+        <f t="shared" ref="L67" si="28">I67*20</f>
+        <v>20</v>
       </c>
       <c r="M67">
         <v>-1</v>
@@ -4742,10 +4742,10 @@
         <v>0</v>
       </c>
       <c r="B68">
-        <v>200</v>
+        <v>-1000</v>
       </c>
       <c r="C68">
-        <v>-2120</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -4757,21 +4757,21 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I68">
         <v>1</v>
       </c>
       <c r="J68">
         <f t="shared" si="20"/>
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="K68">
         <f t="shared" si="21"/>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="L68">
         <f t="shared" si="22"/>
@@ -4798,10 +4798,10 @@
         <v>0</v>
       </c>
       <c r="B69">
-        <v>200</v>
+        <v>-1000</v>
       </c>
       <c r="C69">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4813,21 +4813,21 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>1</v>
       </c>
       <c r="J69">
         <f t="shared" si="20"/>
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="K69">
         <f t="shared" si="21"/>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="L69">
         <f t="shared" si="22"/>
@@ -4854,10 +4854,10 @@
         <v>0</v>
       </c>
       <c r="B70">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C70">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -6334,15 +6334,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="J96:J97" si="29">G96*20</f>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="K96:K97" si="30">H96*20</f>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="L96:L97" si="31">I96*20</f>
         <v>20</v>
       </c>
       <c r="M96">
@@ -6390,15 +6390,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -6446,15 +6446,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="J98" si="32">G98*20</f>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="K98" si="33">H98*20</f>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="L98" si="34">I98*20</f>
         <v>20</v>
       </c>
       <c r="M98">
@@ -6502,15 +6502,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" ref="J99:J100" si="23">G99*20</f>
+        <f t="shared" ref="J99" si="35">G99*20</f>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" ref="K99:K100" si="24">H99*20</f>
+        <f t="shared" ref="K99" si="36">H99*20</f>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" ref="L99:L100" si="25">I99*20</f>
+        <f t="shared" ref="L99" si="37">I99*20</f>
         <v>20</v>
       </c>
       <c r="M99">
@@ -6558,15 +6558,15 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="J100" si="38">G100*20</f>
         <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="K100" si="39">H100*20</f>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L100" si="40">I100*20</f>
         <v>20</v>
       </c>
       <c r="M100">

--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F3CCD3-49EC-45F5-A7DB-8AB593EF34D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C198EE58-3938-4B61-AAFE-ABA851E23D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="B42">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C42">
-        <v>-1900</v>
+        <v>-2360</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -3318,14 +3318,14 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K42">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="L42">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4627,13 +4627,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>3990</v>
+        <v>0</v>
       </c>
       <c r="B66">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="C66">
-        <v>-3030</v>
+        <v>-2120</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4645,17 +4645,17 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H66">
         <v>5</v>
       </c>
       <c r="I66">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J66">
         <f t="shared" si="23"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="K66">
         <f t="shared" si="24"/>
@@ -4663,10 +4663,10 @@
       </c>
       <c r="L66">
         <f t="shared" si="25"/>
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66">
         <v>0</v>
@@ -4683,19 +4683,19 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="B67">
-        <v>-1000</v>
+        <v>200</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>-2360</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4704,10 +4704,10 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J67">
         <f t="shared" ref="J67" si="26">G67*20</f>
@@ -4715,14 +4715,14 @@
       </c>
       <c r="K67">
         <f t="shared" ref="K67" si="27">H67*20</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L67">
         <f t="shared" ref="L67" si="28">I67*20</f>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="M67">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -4739,19 +4739,19 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="B68">
-        <v>-1000</v>
+        <v>200</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>-2360</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -4760,10 +4760,10 @@
         <v>1</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J68">
         <f t="shared" si="20"/>
@@ -4771,14 +4771,14 @@
       </c>
       <c r="K68">
         <f t="shared" si="21"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L68">
         <f t="shared" si="22"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="M68">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -4795,13 +4795,13 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>0</v>
+        <v>3990</v>
       </c>
       <c r="B69">
-        <v>-1000</v>
+        <v>440</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4816,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J69">
         <f t="shared" si="20"/>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="K69">
         <f t="shared" si="21"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L69">
         <f t="shared" si="22"/>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="M69">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N69">
         <v>0</v>

--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C198EE58-3938-4B61-AAFE-ABA851E23D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6C87F45-EAF0-45DE-871B-82143B1AB9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4577,7 +4577,7 @@
         <v>200</v>
       </c>
       <c r="C65">
-        <v>-2600</v>
+        <v>-2620</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="J65">
         <f t="shared" ref="J65:J66" si="23">G65*20</f>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="K65">
         <f t="shared" ref="K65:K66" si="24">H65*20</f>
@@ -4633,7 +4633,7 @@
         <v>200</v>
       </c>
       <c r="C66">
-        <v>-2120</v>
+        <v>-2100</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H66">
         <v>5</v>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="J66">
         <f t="shared" si="23"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="K66">
         <f t="shared" si="24"/>
@@ -4701,25 +4701,23 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H67">
         <v>5</v>
       </c>
       <c r="I67">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" ref="J67" si="26">G67*20</f>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" ref="K67" si="27">H67*20</f>
+        <f t="shared" ref="K67" si="26">H67*20</f>
         <v>100</v>
       </c>
       <c r="L67">
-        <f t="shared" ref="L67" si="28">I67*20</f>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -4757,16 +4755,15 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H68">
         <v>5</v>
       </c>
       <c r="I68">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K68">
@@ -4774,8 +4771,7 @@
         <v>100</v>
       </c>
       <c r="L68">
-        <f t="shared" si="22"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="M68">
         <v>0</v>
@@ -6334,15 +6330,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" ref="J96:J97" si="29">G96*20</f>
+        <f t="shared" ref="J96:J97" si="27">G96*20</f>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" ref="K96:K97" si="30">H96*20</f>
+        <f t="shared" ref="K96:K97" si="28">H96*20</f>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" ref="L96:L97" si="31">I96*20</f>
+        <f t="shared" ref="L96:L97" si="29">I96*20</f>
         <v>20</v>
       </c>
       <c r="M96">
@@ -6390,15 +6386,15 @@
         <v>1</v>
       </c>
       <c r="J97">
+        <f t="shared" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="K97">
+        <f t="shared" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="L97">
         <f t="shared" si="29"/>
-        <v>20</v>
-      </c>
-      <c r="K97">
-        <f t="shared" si="30"/>
-        <v>20</v>
-      </c>
-      <c r="L97">
-        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -6446,15 +6442,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" ref="J98" si="32">G98*20</f>
+        <f t="shared" ref="J98" si="30">G98*20</f>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" ref="K98" si="33">H98*20</f>
+        <f t="shared" ref="K98" si="31">H98*20</f>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" ref="L98" si="34">I98*20</f>
+        <f t="shared" ref="L98" si="32">I98*20</f>
         <v>20</v>
       </c>
       <c r="M98">
@@ -6502,15 +6498,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" ref="J99" si="35">G99*20</f>
+        <f t="shared" ref="J99" si="33">G99*20</f>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" ref="K99" si="36">H99*20</f>
+        <f t="shared" ref="K99" si="34">H99*20</f>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" ref="L99" si="37">I99*20</f>
+        <f t="shared" ref="L99" si="35">I99*20</f>
         <v>20</v>
       </c>
       <c r="M99">
@@ -6558,15 +6554,15 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" ref="J100" si="38">G100*20</f>
+        <f t="shared" ref="J100" si="36">G100*20</f>
         <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" ref="K100" si="39">H100*20</f>
+        <f t="shared" ref="K100" si="37">H100*20</f>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" ref="L100" si="40">I100*20</f>
+        <f t="shared" ref="L100" si="38">I100*20</f>
         <v>20</v>
       </c>
       <c r="M100">

--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6C87F45-EAF0-45DE-871B-82143B1AB9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6DBDB7D-D0BC-4C69-A9C3-1AF875F9A7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4803,22 +4803,21 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H69">
         <v>5</v>
       </c>
       <c r="I69">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J69">
-        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K69">
@@ -4826,8 +4825,7 @@
         <v>100</v>
       </c>
       <c r="L69">
-        <f t="shared" si="22"/>
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="M69">
         <v>1</v>
@@ -4847,46 +4845,44 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>0</v>
+        <v>2970</v>
       </c>
       <c r="B70">
-        <v>-1000</v>
+        <v>440</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I70">
         <v>1</v>
       </c>
       <c r="J70">
-        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="K70">
         <f t="shared" si="21"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L70">
-        <f t="shared" si="22"/>
-        <v>20</v>
+        <v>1040</v>
       </c>
       <c r="M70">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N70">
         <v>0</v>
@@ -4903,13 +4899,13 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B71">
-        <v>-1000</v>
+        <v>440</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>-2520</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4921,28 +4917,28 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I71">
         <v>1</v>
       </c>
       <c r="J71">
         <f t="shared" si="20"/>
-        <v>20</v>
+        <v>1040</v>
       </c>
       <c r="K71">
         <f t="shared" si="21"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L71">
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M71">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N71">
         <v>0</v>
@@ -4959,13 +4955,13 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B72">
-        <v>-1000</v>
+        <v>440</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>-3540</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -4977,28 +4973,28 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I72">
         <v>1</v>
       </c>
       <c r="J72">
         <f t="shared" si="20"/>
-        <v>20</v>
+        <v>1040</v>
       </c>
       <c r="K72">
         <f t="shared" si="21"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L72">
         <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="M72">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N72">
         <v>0</v>

--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6DBDB7D-D0BC-4C69-A9C3-1AF875F9A7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51159743-C369-4F77-8A9D-B4E1E1E359A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -1068,15 +1068,15 @@
         <v>21</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J61" si="1">G2*20</f>
+        <f t="shared" ref="J2:J63" si="1">G2*20</f>
         <v>200</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K61" si="2">H2*20</f>
+        <f t="shared" ref="K2:K63" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L61" si="3">I2*20</f>
+        <f t="shared" ref="L2:L63" si="3">I2*20</f>
         <v>420</v>
       </c>
       <c r="M2">
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="B46">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C46">
         <v>20</v>
@@ -3528,7 +3528,7 @@
         <v>10</v>
       </c>
       <c r="H46">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K46">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L46">
         <f t="shared" si="3"/>
@@ -3566,7 +3566,7 @@
         <v>110</v>
       </c>
       <c r="B47">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C47">
         <v>-1050</v>
@@ -3584,7 +3584,7 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I47">
         <v>106</v>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="K47">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L47">
         <f t="shared" si="3"/>
@@ -3622,7 +3622,7 @@
         <v>-110</v>
       </c>
       <c r="B48">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C48">
         <v>-1050</v>
@@ -3640,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="H48">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I48">
         <v>106</v>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="K48">
         <f t="shared" ref="K48" si="15">H48*20</f>
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L48">
         <f t="shared" ref="L48" si="16">I48*20</f>
@@ -3678,7 +3678,7 @@
         <v>185</v>
       </c>
       <c r="B49">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C49">
         <v>-2100</v>
@@ -3696,7 +3696,7 @@
         <v>6.5</v>
       </c>
       <c r="H49">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="K49">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L49">
         <f t="shared" si="3"/>
@@ -3734,7 +3734,7 @@
         <v>-185</v>
       </c>
       <c r="B50">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C50">
         <v>-2100</v>
@@ -3752,7 +3752,7 @@
         <v>6.5</v>
       </c>
       <c r="H50">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="K50">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L50">
         <f t="shared" si="3"/>
@@ -3790,7 +3790,7 @@
         <v>-260</v>
       </c>
       <c r="B51">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C51">
         <v>-2360</v>
@@ -3808,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="H51">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I51">
         <v>25</v>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="K51">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="L51">
         <f t="shared" si="3"/>
@@ -3846,7 +3846,7 @@
         <v>260</v>
       </c>
       <c r="B52">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C52">
         <v>-2360</v>
@@ -3864,21 +3864,21 @@
         <v>1</v>
       </c>
       <c r="H52">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I52">
         <v>25</v>
       </c>
       <c r="J52">
-        <f t="shared" ref="J52" si="17">G52*20</f>
+        <f t="shared" ref="J52:J53" si="17">G52*20</f>
         <v>20</v>
       </c>
       <c r="K52">
-        <f t="shared" ref="K52" si="18">H52*20</f>
-        <v>250</v>
+        <f t="shared" ref="K52:K53" si="18">H52*20</f>
+        <v>400</v>
       </c>
       <c r="L52">
-        <f t="shared" ref="L52" si="19">I52*20</f>
+        <f t="shared" ref="L52:L53" si="19">I52*20</f>
         <v>500</v>
       </c>
       <c r="M52">
@@ -3899,604 +3899,604 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53">
+        <v>400</v>
+      </c>
+      <c r="C53">
+        <v>-2600</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>25</v>
+      </c>
+      <c r="H53">
+        <v>20</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="17"/>
+        <v>500</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="18"/>
+        <v>400</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="M53">
+        <v>-1</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54">
+        <v>600</v>
+      </c>
+      <c r="C54">
+        <v>-2720</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>10</v>
+      </c>
+      <c r="H54">
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ref="J54" si="20">G54*20</f>
+        <v>200</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ref="K54" si="21">H54*20</f>
+        <v>400</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ref="L54" si="22">I54*20</f>
+        <v>20</v>
+      </c>
+      <c r="M54">
+        <v>-1</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A55">
         <v>110</v>
       </c>
-      <c r="B53">
-        <v>450</v>
-      </c>
-      <c r="C53">
+      <c r="B55">
+        <v>600</v>
+      </c>
+      <c r="C55">
         <v>-2820</v>
       </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-      <c r="H53">
-        <v>12.5</v>
-      </c>
-      <c r="I53">
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>20</v>
+      </c>
+      <c r="I55">
         <v>11</v>
       </c>
-      <c r="J53">
+      <c r="J55">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="K53">
+      <c r="K55">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L53">
+        <v>400</v>
+      </c>
+      <c r="L55">
         <f t="shared" si="3"/>
         <v>220</v>
       </c>
-      <c r="M53">
-        <v>-1</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A54">
+      <c r="M55">
+        <v>-1</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A56">
         <v>-110</v>
       </c>
-      <c r="B54">
-        <v>450</v>
-      </c>
-      <c r="C54">
+      <c r="B56">
+        <v>600</v>
+      </c>
+      <c r="C56">
         <v>-2920</v>
       </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>1</v>
-      </c>
-      <c r="H54">
-        <v>12.5</v>
-      </c>
-      <c r="I54">
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>20</v>
+      </c>
+      <c r="I56">
         <v>21</v>
       </c>
-      <c r="J54">
+      <c r="J56">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="K54">
+      <c r="K56">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L54">
+        <v>400</v>
+      </c>
+      <c r="L56">
         <f t="shared" si="3"/>
         <v>420</v>
       </c>
-      <c r="M54">
-        <v>-1</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A55">
+      <c r="M56">
+        <v>-1</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A57">
         <v>780</v>
       </c>
-      <c r="B55">
-        <v>450</v>
-      </c>
-      <c r="C55">
+      <c r="B57">
+        <v>600</v>
+      </c>
+      <c r="C57">
         <v>-3140</v>
       </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
         <v>88</v>
       </c>
-      <c r="H55">
-        <v>12.5</v>
-      </c>
-      <c r="I55">
-        <v>1</v>
-      </c>
-      <c r="J55">
+      <c r="H57">
+        <v>20</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
         <f t="shared" si="1"/>
         <v>1760</v>
       </c>
-      <c r="K55">
+      <c r="K57">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L55">
+        <v>400</v>
+      </c>
+      <c r="L57">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="M55">
-        <v>-1</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A56">
+      <c r="M57">
+        <v>-1</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A58">
         <v>890</v>
       </c>
-      <c r="B56">
-        <v>450</v>
-      </c>
-      <c r="C56">
+      <c r="B58">
+        <v>600</v>
+      </c>
+      <c r="C58">
         <v>-2920</v>
       </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
         <v>77</v>
       </c>
-      <c r="H56">
-        <v>12.5</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="J56">
+      <c r="H58">
+        <v>20</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
         <f t="shared" si="1"/>
         <v>1540</v>
       </c>
-      <c r="K56">
+      <c r="K58">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L56">
+        <v>400</v>
+      </c>
+      <c r="L58">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="M56">
-        <v>-1</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A57">
+      <c r="M58">
+        <v>-1</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A59">
         <v>1670</v>
       </c>
-      <c r="B57">
-        <v>450</v>
-      </c>
-      <c r="C57">
+      <c r="B59">
+        <v>600</v>
+      </c>
+      <c r="C59">
         <v>-3030</v>
       </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-      <c r="H57">
-        <v>12.5</v>
-      </c>
-      <c r="I57">
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>20</v>
+      </c>
+      <c r="I59">
         <v>10</v>
       </c>
-      <c r="J57">
+      <c r="J59">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="K57">
+      <c r="K59">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L57">
+        <v>400</v>
+      </c>
+      <c r="L59">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="M57">
-        <v>-1</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A58">
+      <c r="M59">
+        <v>-1</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A60">
         <v>2550</v>
       </c>
-      <c r="B58">
-        <v>450</v>
-      </c>
-      <c r="C58">
+      <c r="B60">
+        <v>600</v>
+      </c>
+      <c r="C60">
         <v>-3030</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58">
-        <v>12.5</v>
-      </c>
-      <c r="I58">
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>20</v>
+      </c>
+      <c r="I60">
         <v>10</v>
       </c>
-      <c r="J58">
+      <c r="J60">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="K58">
+      <c r="K60">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L58">
+        <v>400</v>
+      </c>
+      <c r="L60">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="M58">
-        <v>-1</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A59">
+      <c r="M60">
+        <v>-1</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A61">
         <v>2770</v>
       </c>
-      <c r="B59">
-        <v>450</v>
-      </c>
-      <c r="C59">
+      <c r="B61">
+        <v>600</v>
+      </c>
+      <c r="C61">
         <v>-2920</v>
       </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
         <v>21</v>
       </c>
-      <c r="H59">
-        <v>12.5</v>
-      </c>
-      <c r="I59">
-        <v>1</v>
-      </c>
-      <c r="J59">
+      <c r="H61">
+        <v>20</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K59">
+      <c r="K61">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L59">
+        <v>400</v>
+      </c>
+      <c r="L61">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="M59">
-        <v>-1</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A60">
+      <c r="M61">
+        <v>-1</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A62">
         <v>2770</v>
       </c>
-      <c r="B60">
-        <v>450</v>
-      </c>
-      <c r="C60">
+      <c r="B62">
+        <v>600</v>
+      </c>
+      <c r="C62">
         <v>-3140</v>
       </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
         <v>21</v>
       </c>
-      <c r="H60">
-        <v>12.5</v>
-      </c>
-      <c r="I60">
-        <v>1</v>
-      </c>
-      <c r="J60">
+      <c r="H62">
+        <v>20</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K60">
+      <c r="K62">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L60">
+        <v>400</v>
+      </c>
+      <c r="L62">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="M60">
-        <v>-1</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A61">
+      <c r="M62">
+        <v>-1</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A63">
         <v>2970</v>
       </c>
-      <c r="B61">
-        <v>450</v>
-      </c>
-      <c r="C61">
+      <c r="B63">
+        <v>600</v>
+      </c>
+      <c r="C63">
         <v>-2720</v>
       </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>12.5</v>
-      </c>
-      <c r="I61">
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>20</v>
+      </c>
+      <c r="I63">
         <v>19</v>
       </c>
-      <c r="J61">
+      <c r="J63">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="K61">
+      <c r="K63">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="L61">
+        <v>400</v>
+      </c>
+      <c r="L63">
         <f t="shared" si="3"/>
         <v>380</v>
       </c>
-      <c r="M61">
-        <v>-1</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A62">
-        <v>2970</v>
-      </c>
-      <c r="B62">
-        <v>450</v>
-      </c>
-      <c r="C62">
-        <v>-3340</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62">
-        <v>12.5</v>
-      </c>
-      <c r="I62">
-        <v>19</v>
-      </c>
-      <c r="J62">
-        <f t="shared" ref="J62:J95" si="20">G62*20</f>
-        <v>20</v>
-      </c>
-      <c r="K62">
-        <f t="shared" ref="K62:K95" si="21">H62*20</f>
-        <v>250</v>
-      </c>
-      <c r="L62">
-        <f t="shared" ref="L62:L95" si="22">I62*20</f>
-        <v>380</v>
-      </c>
-      <c r="M62">
-        <v>-1</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A63">
-        <v>3480</v>
-      </c>
-      <c r="B63">
-        <v>450</v>
-      </c>
-      <c r="C63">
-        <v>-2520</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <v>50</v>
-      </c>
-      <c r="H63">
-        <v>12.5</v>
-      </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="J63">
-        <f t="shared" si="20"/>
-        <v>1000</v>
-      </c>
-      <c r="K63">
-        <f t="shared" si="21"/>
-        <v>250</v>
-      </c>
-      <c r="L63">
-        <f t="shared" si="22"/>
-        <v>20</v>
-      </c>
       <c r="M63">
         <v>-1</v>
       </c>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>3480</v>
+        <v>2970</v>
       </c>
       <c r="B64">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="C64">
-        <v>-3540</v>
+        <v>-3340</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -4533,25 +4533,25 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I64">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J64">
-        <f t="shared" si="20"/>
-        <v>1000</v>
+        <f t="shared" ref="J64:J97" si="23">G64*20</f>
+        <v>20</v>
       </c>
       <c r="K64">
-        <f t="shared" si="21"/>
-        <v>250</v>
+        <f t="shared" ref="K64:K97" si="24">H64*20</f>
+        <v>400</v>
       </c>
       <c r="L64">
-        <f t="shared" si="22"/>
-        <v>20</v>
+        <f t="shared" ref="L64:L97" si="25">I64*20</f>
+        <v>380</v>
       </c>
       <c r="M64">
         <v>-1</v>
@@ -4571,13 +4571,13 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B65">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C65">
-        <v>-2620</v>
+        <v>-2520</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -4589,28 +4589,28 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="H65">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" ref="J65:J66" si="23">G65*20</f>
-        <v>540</v>
+        <f t="shared" si="23"/>
+        <v>1000</v>
       </c>
       <c r="K65">
-        <f t="shared" ref="K65:K66" si="24">H65*20</f>
-        <v>100</v>
+        <f t="shared" si="24"/>
+        <v>400</v>
       </c>
       <c r="L65">
-        <f t="shared" ref="L65:L66" si="25">I65*20</f>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -4627,13 +4627,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B66">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C66">
-        <v>-2100</v>
+        <v>-3540</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4645,28 +4645,28 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I66">
         <v>1</v>
       </c>
       <c r="J66">
         <f t="shared" si="23"/>
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="K66">
         <f t="shared" si="24"/>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L66">
         <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N66">
         <v>0</v>
@@ -4683,25 +4683,25 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B67">
         <v>200</v>
       </c>
       <c r="C67">
-        <v>-2360</v>
+        <v>-2600</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H67">
         <v>5</v>
@@ -4710,14 +4710,16 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>20</v>
+        <f t="shared" ref="J67:J68" si="26">G67*20</f>
+        <v>500</v>
       </c>
       <c r="K67">
-        <f t="shared" ref="K67" si="26">H67*20</f>
+        <f t="shared" ref="K67:K68" si="27">H67*20</f>
         <v>100</v>
       </c>
       <c r="L67">
-        <v>540</v>
+        <f t="shared" ref="L67:L68" si="28">I67*20</f>
+        <v>20</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -4737,25 +4739,25 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>-260</v>
+        <v>0</v>
       </c>
       <c r="B68">
         <v>200</v>
       </c>
       <c r="C68">
-        <v>-2360</v>
+        <v>-2120</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H68">
         <v>5</v>
@@ -4764,14 +4766,16 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>20</v>
+        <f t="shared" si="26"/>
+        <v>500</v>
       </c>
       <c r="K68">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>100</v>
       </c>
       <c r="L68">
-        <v>540</v>
+        <f t="shared" si="28"/>
+        <v>20</v>
       </c>
       <c r="M68">
         <v>0</v>
@@ -4791,13 +4795,13 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>3990</v>
+        <v>240</v>
       </c>
       <c r="B69">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="C69">
-        <v>-3030</v>
+        <v>-2360</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4809,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="H69">
         <v>5</v>
@@ -4821,14 +4825,14 @@
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="K69" si="29">H69*20</f>
         <v>100</v>
       </c>
       <c r="L69">
-        <v>1040</v>
+        <v>500</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69">
         <v>0</v>
@@ -4845,13 +4849,13 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>2970</v>
+        <v>-240</v>
       </c>
       <c r="B70">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="C70">
-        <v>-3030</v>
+        <v>-2360</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4863,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -4875,14 +4879,14 @@
         <v>20</v>
       </c>
       <c r="K70">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>100</v>
       </c>
       <c r="L70">
-        <v>1040</v>
+        <v>500</v>
       </c>
       <c r="M70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70">
         <v>0</v>
@@ -4899,19 +4903,19 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>3480</v>
+        <v>3990</v>
       </c>
       <c r="B71">
         <v>440</v>
       </c>
       <c r="C71">
-        <v>-2520</v>
+        <v>-3030</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -4926,16 +4930,14 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="24"/>
+        <v>100</v>
+      </c>
+      <c r="L71">
         <v>1040</v>
-      </c>
-      <c r="K71">
-        <f t="shared" si="21"/>
-        <v>100</v>
-      </c>
-      <c r="L71">
-        <f t="shared" si="22"/>
-        <v>20</v>
       </c>
       <c r="M71">
         <v>1</v>
@@ -4955,19 +4957,19 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>3480</v>
+        <v>2970</v>
       </c>
       <c r="B72">
         <v>440</v>
       </c>
       <c r="C72">
-        <v>-3540</v>
+        <v>-3030</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -4982,16 +4984,14 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="24"/>
+        <v>100</v>
+      </c>
+      <c r="L72">
         <v>1040</v>
-      </c>
-      <c r="K72">
-        <f t="shared" si="21"/>
-        <v>100</v>
-      </c>
-      <c r="L72">
-        <f t="shared" si="22"/>
-        <v>20</v>
       </c>
       <c r="M72">
         <v>1</v>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B73">
-        <v>-1000</v>
+        <v>440</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>-2520</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -5029,28 +5029,28 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I73">
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="20"/>
-        <v>20</v>
+        <f t="shared" si="23"/>
+        <v>1040</v>
       </c>
       <c r="K73">
-        <f t="shared" si="21"/>
-        <v>20</v>
+        <f t="shared" si="24"/>
+        <v>100</v>
       </c>
       <c r="L73">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M73">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -5067,13 +5067,13 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B74">
-        <v>-1000</v>
+        <v>440</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>-3540</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -5085,28 +5085,28 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I74">
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="20"/>
-        <v>20</v>
+        <f t="shared" si="23"/>
+        <v>1040</v>
       </c>
       <c r="K74">
-        <f t="shared" si="21"/>
-        <v>20</v>
+        <f t="shared" si="24"/>
+        <v>100</v>
       </c>
       <c r="L74">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M74">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N74">
         <v>0</v>
@@ -5150,15 +5150,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -5206,15 +5206,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -5262,15 +5262,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -5318,15 +5318,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -5374,15 +5374,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -5430,15 +5430,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -5486,15 +5486,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -5542,15 +5542,15 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M82">
@@ -5598,15 +5598,15 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M83">
@@ -5654,15 +5654,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -5710,15 +5710,15 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M85">
@@ -5766,15 +5766,15 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M86">
@@ -5822,15 +5822,15 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M87">
@@ -5878,15 +5878,15 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M88">
@@ -5934,15 +5934,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5990,15 +5990,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -6046,15 +6046,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M91">
@@ -6102,15 +6102,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M92">
@@ -6158,15 +6158,15 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M93">
@@ -6214,15 +6214,15 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M94">
@@ -6270,15 +6270,15 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M95">
@@ -6326,15 +6326,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" ref="J96:J97" si="27">G96*20</f>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" ref="K96:K97" si="28">H96*20</f>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" ref="L96:L97" si="29">I96*20</f>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -6382,15 +6382,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -6438,15 +6438,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" ref="J98" si="30">G98*20</f>
+        <f t="shared" ref="J98:J99" si="30">G98*20</f>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" ref="K98" si="31">H98*20</f>
+        <f t="shared" ref="K98:K99" si="31">H98*20</f>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" ref="L98" si="32">I98*20</f>
+        <f t="shared" ref="L98:L99" si="32">I98*20</f>
         <v>20</v>
       </c>
       <c r="M98">
@@ -6494,15 +6494,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" ref="J99" si="33">G99*20</f>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" ref="K99" si="34">H99*20</f>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" ref="L99" si="35">I99*20</f>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M99">
@@ -6550,15 +6550,15 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" ref="J100" si="36">G100*20</f>
+        <f t="shared" ref="J100" si="33">G100*20</f>
         <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" ref="K100" si="37">H100*20</f>
+        <f t="shared" ref="K100" si="34">H100*20</f>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" ref="L100" si="38">I100*20</f>
+        <f t="shared" ref="L100" si="35">I100*20</f>
         <v>20</v>
       </c>
       <c r="M100">
@@ -6574,6 +6574,62 @@
         <v>0</v>
       </c>
       <c r="Q100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>0</v>
+      </c>
+      <c r="B101">
+        <v>-1000</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <f t="shared" ref="J101" si="36">G101*20</f>
+        <v>20</v>
+      </c>
+      <c r="K101">
+        <f t="shared" ref="K101" si="37">H101*20</f>
+        <v>20</v>
+      </c>
+      <c r="L101">
+        <f t="shared" ref="L101" si="38">I101*20</f>
+        <v>20</v>
+      </c>
+      <c r="M101">
+        <v>-1</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51159743-C369-4F77-8A9D-B4E1E1E359A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01AB5504-026B-4797-9FF5-B26416A17EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -1068,15 +1068,15 @@
         <v>21</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J63" si="1">G2*20</f>
+        <f t="shared" ref="J2:J57" si="1">G2*20</f>
         <v>200</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K63" si="2">H2*20</f>
+        <f t="shared" ref="K2:K57" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L63" si="3">I2*20</f>
+        <f t="shared" ref="L2:L57" si="3">I2*20</f>
         <v>420</v>
       </c>
       <c r="M2">
@@ -3675,42 +3675,42 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A49">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="B49">
+        <v>600</v>
+      </c>
+      <c r="C49">
+        <v>-2720</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+      <c r="H49">
+        <v>20</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <f t="shared" ref="J49" si="17">G49*20</f>
+        <v>200</v>
+      </c>
+      <c r="K49">
+        <f t="shared" ref="K49" si="18">H49*20</f>
         <v>400</v>
       </c>
-      <c r="C49">
-        <v>-2100</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>6.5</v>
-      </c>
-      <c r="H49">
-        <v>20</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="J49">
-        <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="K49">
-        <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
       <c r="L49">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L49" si="19">I49*20</f>
         <v>20</v>
       </c>
       <c r="M49">
@@ -3731,13 +3731,13 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>-185</v>
+        <v>110</v>
       </c>
       <c r="B50">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C50">
-        <v>-2100</v>
+        <v>-2820</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3749,17 +3749,17 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>20</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J50">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="K50">
         <f t="shared" si="2"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L50">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="M50">
         <v>-1</v>
@@ -3787,13 +3787,13 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>-260</v>
+        <v>-110</v>
       </c>
       <c r="B51">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C51">
-        <v>-2360</v>
+        <v>-2920</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>20</v>
       </c>
       <c r="I51">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J51">
         <f t="shared" si="1"/>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="L51">
         <f t="shared" si="3"/>
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="M51">
         <v>-1</v>
@@ -3843,43 +3843,43 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A52">
-        <v>260</v>
+        <v>780</v>
       </c>
       <c r="B52">
+        <v>600</v>
+      </c>
+      <c r="C52">
+        <v>-3140</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>88</v>
+      </c>
+      <c r="H52">
+        <v>20</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="1"/>
+        <v>1760</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="C52">
-        <v>-2360</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-      <c r="H52">
-        <v>20</v>
-      </c>
-      <c r="I52">
-        <v>25</v>
-      </c>
-      <c r="J52">
-        <f t="shared" ref="J52:J53" si="17">G52*20</f>
-        <v>20</v>
-      </c>
-      <c r="K52">
-        <f t="shared" ref="K52:K53" si="18">H52*20</f>
-        <v>400</v>
-      </c>
       <c r="L52">
-        <f t="shared" ref="L52:L53" si="19">I52*20</f>
-        <v>500</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M52">
         <v>-1</v>
@@ -3899,42 +3899,42 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="B53">
+        <v>600</v>
+      </c>
+      <c r="C53">
+        <v>-2920</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>77</v>
+      </c>
+      <c r="H53">
+        <v>20</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="1"/>
+        <v>1540</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="C53">
-        <v>-2600</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>25</v>
-      </c>
-      <c r="H53">
-        <v>20</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="J53">
-        <f t="shared" si="17"/>
-        <v>500</v>
-      </c>
-      <c r="K53">
-        <f t="shared" si="18"/>
-        <v>400</v>
-      </c>
       <c r="L53">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M53">
@@ -3955,13 +3955,13 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A54">
-        <v>0</v>
+        <v>1670</v>
       </c>
       <c r="B54">
         <v>600</v>
       </c>
       <c r="C54">
-        <v>-2720</v>
+        <v>-3030</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3973,25 +3973,25 @@
         <v>0</v>
       </c>
       <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>20</v>
+      </c>
+      <c r="I54">
         <v>10</v>
       </c>
-      <c r="H54">
-        <v>20</v>
-      </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
       <c r="J54">
-        <f t="shared" ref="J54" si="20">G54*20</f>
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="3"/>
         <v>200</v>
-      </c>
-      <c r="K54">
-        <f t="shared" ref="K54" si="21">H54*20</f>
-        <v>400</v>
-      </c>
-      <c r="L54">
-        <f t="shared" ref="L54" si="22">I54*20</f>
-        <v>20</v>
       </c>
       <c r="M54">
         <v>-1</v>
@@ -4011,13 +4011,13 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>110</v>
+        <v>2550</v>
       </c>
       <c r="B55">
         <v>600</v>
       </c>
       <c r="C55">
-        <v>-2820</v>
+        <v>-3030</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -4035,19 +4035,19 @@
         <v>20</v>
       </c>
       <c r="I55">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J55">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J55" si="20">G55*20</f>
         <v>20</v>
       </c>
       <c r="K55">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K55" si="21">H55*20</f>
         <v>400</v>
       </c>
       <c r="L55">
-        <f t="shared" si="3"/>
-        <v>220</v>
+        <f t="shared" ref="L55" si="22">I55*20</f>
+        <v>200</v>
       </c>
       <c r="M55">
         <v>-1</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>-110</v>
+        <v>2770</v>
       </c>
       <c r="B56">
         <v>600</v>
@@ -4085,25 +4085,25 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H56">
         <v>20</v>
       </c>
       <c r="I56">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J56">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" ref="J56:J57" si="23">G56*20</f>
+        <v>420</v>
       </c>
       <c r="K56">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K56:K57" si="24">H56*20</f>
         <v>400</v>
       </c>
       <c r="L56">
-        <f t="shared" si="3"/>
-        <v>420</v>
+        <f t="shared" ref="L56:L57" si="25">I56*20</f>
+        <v>20</v>
       </c>
       <c r="M56">
         <v>-1</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>780</v>
+        <v>2770</v>
       </c>
       <c r="B57">
         <v>600</v>
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="H57">
         <v>20</v>
@@ -4150,15 +4150,15 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <f t="shared" si="1"/>
-        <v>1760</v>
+        <f t="shared" si="23"/>
+        <v>420</v>
       </c>
       <c r="K57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>400</v>
       </c>
       <c r="L57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="M57">
@@ -4179,13 +4179,13 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="B58">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="C58">
-        <v>-2920</v>
+        <v>-2600</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -4197,28 +4197,28 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I58">
         <v>1</v>
       </c>
       <c r="J58">
-        <f t="shared" si="1"/>
-        <v>1540</v>
+        <f t="shared" ref="J58:J59" si="26">G58*20</f>
+        <v>500</v>
       </c>
       <c r="K58">
-        <f t="shared" si="2"/>
-        <v>400</v>
+        <f t="shared" ref="K58:K59" si="27">H58*20</f>
+        <v>100</v>
       </c>
       <c r="L58">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L58:L59" si="28">I58*20</f>
         <v>20</v>
       </c>
       <c r="M58">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -4235,13 +4235,13 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>1670</v>
+        <v>0</v>
       </c>
       <c r="B59">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="C59">
-        <v>-3030</v>
+        <v>-2120</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -4253,28 +4253,28 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H59">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I59">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="26"/>
+        <v>500</v>
       </c>
       <c r="K59">
-        <f t="shared" si="2"/>
-        <v>400</v>
+        <f t="shared" si="27"/>
+        <v>100</v>
       </c>
       <c r="L59">
-        <f t="shared" si="3"/>
-        <v>200</v>
+        <f t="shared" si="28"/>
+        <v>20</v>
       </c>
       <c r="M59">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -4291,46 +4291,44 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>2550</v>
+        <v>240</v>
       </c>
       <c r="B60">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="C60">
-        <v>-3030</v>
+        <v>-2360</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H60">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K60">
-        <f t="shared" si="2"/>
-        <v>400</v>
+        <f t="shared" ref="K60" si="29">H60*20</f>
+        <v>100</v>
       </c>
       <c r="L60">
-        <f t="shared" si="3"/>
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="M60">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -4347,46 +4345,44 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>2770</v>
+        <v>-240</v>
       </c>
       <c r="B61">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="C61">
-        <v>-2920</v>
+        <v>-2360</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H61">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I61">
         <v>1</v>
       </c>
       <c r="J61">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="K61">
-        <f t="shared" si="2"/>
-        <v>400</v>
+        <f t="shared" ref="K61:K88" si="30">H61*20</f>
+        <v>100</v>
       </c>
       <c r="L61">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="M61">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N61">
         <v>0</v>
@@ -4403,46 +4399,44 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>2770</v>
+        <v>3990</v>
       </c>
       <c r="B62">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="C62">
-        <v>-3140</v>
+        <v>-3030</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H62">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I62">
         <v>1</v>
       </c>
       <c r="J62">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="K62">
-        <f t="shared" si="2"/>
-        <v>400</v>
+        <f t="shared" si="30"/>
+        <v>100</v>
       </c>
       <c r="L62">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <v>1040</v>
       </c>
       <c r="M62">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -4462,43 +4456,41 @@
         <v>2970</v>
       </c>
       <c r="B63">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="C63">
-        <v>-2720</v>
+        <v>-3030</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H63">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I63">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K63">
-        <f t="shared" si="2"/>
-        <v>400</v>
+        <f t="shared" si="30"/>
+        <v>100</v>
       </c>
       <c r="L63">
-        <f t="shared" si="3"/>
-        <v>380</v>
+        <v>1040</v>
       </c>
       <c r="M63">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N63">
         <v>0</v>
@@ -4515,13 +4507,13 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>2970</v>
+        <v>3480</v>
       </c>
       <c r="B64">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="C64">
-        <v>-3340</v>
+        <v>-2520</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -4533,28 +4525,28 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H64">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J97" si="23">G64*20</f>
-        <v>20</v>
+        <f t="shared" ref="J64:J88" si="31">G64*20</f>
+        <v>1040</v>
       </c>
       <c r="K64">
-        <f t="shared" ref="K64:K97" si="24">H64*20</f>
-        <v>400</v>
+        <f t="shared" si="30"/>
+        <v>100</v>
       </c>
       <c r="L64">
-        <f t="shared" ref="L64:L97" si="25">I64*20</f>
-        <v>380</v>
+        <f t="shared" ref="L64:L88" si="32">I64*20</f>
+        <v>20</v>
       </c>
       <c r="M64">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -4574,10 +4566,10 @@
         <v>3480</v>
       </c>
       <c r="B65">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="C65">
-        <v>-2520</v>
+        <v>-3540</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -4589,28 +4581,28 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H65">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" si="23"/>
-        <v>1000</v>
+        <f t="shared" si="31"/>
+        <v>1040</v>
       </c>
       <c r="K65">
-        <f t="shared" si="24"/>
-        <v>400</v>
+        <f t="shared" si="30"/>
+        <v>100</v>
       </c>
       <c r="L65">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M65">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -4627,13 +4619,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>3480</v>
+        <v>0</v>
       </c>
       <c r="B66">
-        <v>600</v>
+        <v>-1000</v>
       </c>
       <c r="C66">
-        <v>-3540</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4645,24 +4637,24 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="23"/>
-        <v>1000</v>
+        <f t="shared" si="31"/>
+        <v>20</v>
       </c>
       <c r="K66">
-        <f t="shared" si="24"/>
-        <v>400</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M66">
@@ -4686,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="B67">
-        <v>200</v>
+        <v>-1000</v>
       </c>
       <c r="C67">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -4701,28 +4693,28 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" ref="J67:J68" si="26">G67*20</f>
-        <v>500</v>
+        <f t="shared" si="31"/>
+        <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" ref="K67:K68" si="27">H67*20</f>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" ref="L67:L68" si="28">I67*20</f>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -4742,10 +4734,10 @@
         <v>0</v>
       </c>
       <c r="B68">
-        <v>200</v>
+        <v>-1000</v>
       </c>
       <c r="C68">
-        <v>-2120</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -4757,28 +4749,28 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I68">
         <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="26"/>
-        <v>500</v>
+        <f t="shared" si="31"/>
+        <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="27"/>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -4795,44 +4787,46 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="B69">
-        <v>200</v>
+        <v>-1000</v>
       </c>
       <c r="C69">
-        <v>-2360</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>1</v>
       </c>
       <c r="J69">
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" ref="K69" si="29">H69*20</f>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L69">
-        <v>500</v>
+        <f t="shared" si="32"/>
+        <v>20</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N69">
         <v>0</v>
@@ -4849,44 +4843,46 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>-240</v>
+        <v>0</v>
       </c>
       <c r="B70">
-        <v>200</v>
+        <v>-1000</v>
       </c>
       <c r="C70">
-        <v>-2360</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>1</v>
       </c>
       <c r="J70">
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K70">
-        <f t="shared" si="24"/>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L70">
-        <v>500</v>
+        <f t="shared" si="32"/>
+        <v>20</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N70">
         <v>0</v>
@@ -4903,44 +4899,46 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>3990</v>
+        <v>0</v>
       </c>
       <c r="B71">
-        <v>440</v>
+        <v>-1000</v>
       </c>
       <c r="C71">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I71">
         <v>1</v>
       </c>
       <c r="J71">
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K71">
-        <f t="shared" si="24"/>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L71">
-        <v>1040</v>
+        <f t="shared" si="32"/>
+        <v>20</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N71">
         <v>0</v>
@@ -4957,44 +4955,46 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>2970</v>
+        <v>0</v>
       </c>
       <c r="B72">
-        <v>440</v>
+        <v>-1000</v>
       </c>
       <c r="C72">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>1</v>
       </c>
       <c r="J72">
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K72">
-        <f t="shared" si="24"/>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L72">
-        <v>1040</v>
+        <f t="shared" si="32"/>
+        <v>20</v>
       </c>
       <c r="M72">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>3480</v>
+        <v>0</v>
       </c>
       <c r="B73">
-        <v>440</v>
+        <v>-1000</v>
       </c>
       <c r="C73">
-        <v>-2520</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -5029,28 +5029,28 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="23"/>
-        <v>1040</v>
+        <f t="shared" si="31"/>
+        <v>20</v>
       </c>
       <c r="K73">
-        <f t="shared" si="24"/>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M73">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -5067,13 +5067,13 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>3480</v>
+        <v>0</v>
       </c>
       <c r="B74">
-        <v>440</v>
+        <v>-1000</v>
       </c>
       <c r="C74">
-        <v>-3540</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -5085,28 +5085,28 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="23"/>
-        <v>1040</v>
+        <f t="shared" si="31"/>
+        <v>20</v>
       </c>
       <c r="K74">
-        <f t="shared" si="24"/>
-        <v>100</v>
+        <f t="shared" si="30"/>
+        <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M74">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N74">
         <v>0</v>
@@ -5150,15 +5150,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -5206,15 +5206,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -5262,15 +5262,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -5318,15 +5318,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -5374,15 +5374,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -5430,15 +5430,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -5486,15 +5486,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -5542,15 +5542,15 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M82">
@@ -5598,15 +5598,15 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M83">
@@ -5654,15 +5654,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -5710,15 +5710,15 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M85">
@@ -5766,15 +5766,15 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M86">
@@ -5822,15 +5822,15 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M87">
@@ -5878,15 +5878,15 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M88">
@@ -5934,15 +5934,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="J89:J90" si="33">G89*20</f>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="K89:K90" si="34">H89*20</f>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L89:L90" si="35">I89*20</f>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5990,15 +5990,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -6046,15 +6046,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="J91" si="36">G91*20</f>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="K91" si="37">H91*20</f>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L91" si="38">I91*20</f>
         <v>20</v>
       </c>
       <c r="M91">
@@ -6102,15 +6102,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="J92" si="39">G92*20</f>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="K92" si="40">H92*20</f>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L92" si="41">I92*20</f>
         <v>20</v>
       </c>
       <c r="M92">
@@ -6126,510 +6126,6 @@
         <v>0</v>
       </c>
       <c r="Q92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A93">
-        <v>0</v>
-      </c>
-      <c r="B93">
-        <v>-1000</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-      <c r="D93">
-        <v>0</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>1</v>
-      </c>
-      <c r="H93">
-        <v>1</v>
-      </c>
-      <c r="I93">
-        <v>1</v>
-      </c>
-      <c r="J93">
-        <f t="shared" si="23"/>
-        <v>20</v>
-      </c>
-      <c r="K93">
-        <f t="shared" si="24"/>
-        <v>20</v>
-      </c>
-      <c r="L93">
-        <f t="shared" si="25"/>
-        <v>20</v>
-      </c>
-      <c r="M93">
-        <v>-1</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A94">
-        <v>0</v>
-      </c>
-      <c r="B94">
-        <v>-1000</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-      <c r="D94">
-        <v>0</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <v>0</v>
-      </c>
-      <c r="G94">
-        <v>1</v>
-      </c>
-      <c r="H94">
-        <v>1</v>
-      </c>
-      <c r="I94">
-        <v>1</v>
-      </c>
-      <c r="J94">
-        <f t="shared" si="23"/>
-        <v>20</v>
-      </c>
-      <c r="K94">
-        <f t="shared" si="24"/>
-        <v>20</v>
-      </c>
-      <c r="L94">
-        <f t="shared" si="25"/>
-        <v>20</v>
-      </c>
-      <c r="M94">
-        <v>-1</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A95">
-        <v>0</v>
-      </c>
-      <c r="B95">
-        <v>-1000</v>
-      </c>
-      <c r="C95">
-        <v>0</v>
-      </c>
-      <c r="D95">
-        <v>0</v>
-      </c>
-      <c r="E95">
-        <v>0</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
-      <c r="H95">
-        <v>1</v>
-      </c>
-      <c r="I95">
-        <v>1</v>
-      </c>
-      <c r="J95">
-        <f t="shared" si="23"/>
-        <v>20</v>
-      </c>
-      <c r="K95">
-        <f t="shared" si="24"/>
-        <v>20</v>
-      </c>
-      <c r="L95">
-        <f t="shared" si="25"/>
-        <v>20</v>
-      </c>
-      <c r="M95">
-        <v>-1</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A96">
-        <v>0</v>
-      </c>
-      <c r="B96">
-        <v>-1000</v>
-      </c>
-      <c r="C96">
-        <v>0</v>
-      </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>1</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96">
-        <f t="shared" si="23"/>
-        <v>20</v>
-      </c>
-      <c r="K96">
-        <f t="shared" si="24"/>
-        <v>20</v>
-      </c>
-      <c r="L96">
-        <f t="shared" si="25"/>
-        <v>20</v>
-      </c>
-      <c r="M96">
-        <v>-1</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A97">
-        <v>0</v>
-      </c>
-      <c r="B97">
-        <v>-1000</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-      <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97">
-        <v>1</v>
-      </c>
-      <c r="I97">
-        <v>1</v>
-      </c>
-      <c r="J97">
-        <f t="shared" si="23"/>
-        <v>20</v>
-      </c>
-      <c r="K97">
-        <f t="shared" si="24"/>
-        <v>20</v>
-      </c>
-      <c r="L97">
-        <f t="shared" si="25"/>
-        <v>20</v>
-      </c>
-      <c r="M97">
-        <v>-1</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A98">
-        <v>0</v>
-      </c>
-      <c r="B98">
-        <v>-1000</v>
-      </c>
-      <c r="C98">
-        <v>0</v>
-      </c>
-      <c r="D98">
-        <v>0</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
-      </c>
-      <c r="F98">
-        <v>0</v>
-      </c>
-      <c r="G98">
-        <v>1</v>
-      </c>
-      <c r="H98">
-        <v>1</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98">
-        <f t="shared" ref="J98:J99" si="30">G98*20</f>
-        <v>20</v>
-      </c>
-      <c r="K98">
-        <f t="shared" ref="K98:K99" si="31">H98*20</f>
-        <v>20</v>
-      </c>
-      <c r="L98">
-        <f t="shared" ref="L98:L99" si="32">I98*20</f>
-        <v>20</v>
-      </c>
-      <c r="M98">
-        <v>-1</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A99">
-        <v>0</v>
-      </c>
-      <c r="B99">
-        <v>-1000</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-      <c r="G99">
-        <v>1</v>
-      </c>
-      <c r="H99">
-        <v>1</v>
-      </c>
-      <c r="I99">
-        <v>1</v>
-      </c>
-      <c r="J99">
-        <f t="shared" si="30"/>
-        <v>20</v>
-      </c>
-      <c r="K99">
-        <f t="shared" si="31"/>
-        <v>20</v>
-      </c>
-      <c r="L99">
-        <f t="shared" si="32"/>
-        <v>20</v>
-      </c>
-      <c r="M99">
-        <v>-1</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A100">
-        <v>0</v>
-      </c>
-      <c r="B100">
-        <v>-1000</v>
-      </c>
-      <c r="C100">
-        <v>0</v>
-      </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
-      <c r="H100">
-        <v>1</v>
-      </c>
-      <c r="I100">
-        <v>1</v>
-      </c>
-      <c r="J100">
-        <f t="shared" ref="J100" si="33">G100*20</f>
-        <v>20</v>
-      </c>
-      <c r="K100">
-        <f t="shared" ref="K100" si="34">H100*20</f>
-        <v>20</v>
-      </c>
-      <c r="L100">
-        <f t="shared" ref="L100" si="35">I100*20</f>
-        <v>20</v>
-      </c>
-      <c r="M100">
-        <v>-1</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A101">
-        <v>0</v>
-      </c>
-      <c r="B101">
-        <v>-1000</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-      <c r="E101">
-        <v>0</v>
-      </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>1</v>
-      </c>
-      <c r="I101">
-        <v>1</v>
-      </c>
-      <c r="J101">
-        <f t="shared" ref="J101" si="36">G101*20</f>
-        <v>20</v>
-      </c>
-      <c r="K101">
-        <f t="shared" ref="K101" si="37">H101*20</f>
-        <v>20</v>
-      </c>
-      <c r="L101">
-        <f t="shared" ref="L101" si="38">I101*20</f>
-        <v>20</v>
-      </c>
-      <c r="M101">
-        <v>-1</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Platform1/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01AB5504-026B-4797-9FF5-B26416A17EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D183273-FAD9-41CF-A8D4-30319DC75EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -1068,15 +1068,15 @@
         <v>21</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J57" si="1">G2*20</f>
+        <f t="shared" ref="J2:J54" si="1">G2*20</f>
         <v>200</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K57" si="2">H2*20</f>
+        <f t="shared" ref="K2:K54" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L57" si="3">I2*20</f>
+        <f t="shared" ref="L2:L54" si="3">I2*20</f>
         <v>420</v>
       </c>
       <c r="M2">
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="J58">
         <f t="shared" ref="J58:J59" si="26">G58*20</f>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="K58">
         <f t="shared" ref="K58:K59" si="27">H58*20</f>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="J59">
         <f t="shared" si="26"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="K59">
         <f t="shared" si="27"/>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="B60">
         <v>200</v>
@@ -4345,7 +4345,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>-240</v>
+        <v>-260</v>
       </c>
       <c r="B61">
         <v>200</v>
